--- a/resource-mapping/HoyaDocs-UWorld-QID-Mapping.xlsx
+++ b/resource-mapping/HoyaDocs-UWorld-QID-Mapping.xlsx
@@ -541,7 +541,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UWorld QID → In-House Lecture + Learning Objective Mapping — Endocrine</t>
+          <t>UWorld QID → In-House Lecture + Learning Objective Mapping — Endocrine · v1.0 (2026-04-21)</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>QID Distribution Summary — Endocrine Block</t>
+          <t>QID Distribution Summary — Endocrine Block · v1.0 (2026-04-21)</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Complete QID Mapping with Learning Objectives — Endocrine Block</t>
+          <t>Complete QID Mapping with Learning Objectives — Endocrine Block · v1.0 (2026-04-21)</t>
         </is>
       </c>
     </row>
